--- a/output/pdf_financials_xlsx/BMV.xlsx
+++ b/output/pdf_financials_xlsx/BMV.xlsx
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.510804</v>
+        <v>-1.510804</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.519974</v>
+        <v>-0.519974</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-2.575085</v>
@@ -1270,10 +1270,10 @@
         <v>-0.398434</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.142938</v>
+        <v>-0.142938</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.308383</v>
+        <v>-0.308383</v>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.510804</v>
+        <v>-1.510804</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.519974</v>
+        <v>-0.519974</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-2.575085</v>
@@ -1538,10 +1538,10 @@
         <v>-0.398434</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.142938</v>
+        <v>-0.142938</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.308383</v>
+        <v>-0.308383</v>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.510804</v>
+        <v>-1.510804</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.519974</v>
+        <v>-0.519974</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-2.575085</v>
@@ -1709,10 +1709,10 @@
         <v>-0.398434</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.142938</v>
+        <v>-0.142938</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.308383</v>
+        <v>-0.308383</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.384713</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>37.7701</v>
+        <v>-37.7701</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.510804</v>
+        <v>-1.510804</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.519974</v>
+        <v>-0.519974</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.575085</v>
@@ -1947,10 +1947,10 @@
         <v>-0.398434</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.142938</v>
+        <v>-0.142938</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.308383</v>
+        <v>-0.308383</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.510804</v>
+        <v>-1.510804</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.519974</v>
+        <v>-0.519974</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.575085</v>
@@ -2061,10 +2061,10 @@
         <v>-0.398434</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.142938</v>
+        <v>-0.142938</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.308383</v>
+        <v>-0.308383</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -2195,10 +2195,10 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
@@ -5250,37 +5250,37 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.083425</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.330346</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.415246</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.415246</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.415246</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.415246</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.054696</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.142496</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.352496</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.43756</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.456082</v>
       </c>
     </row>
     <row r="93">
@@ -9044,7 +9044,11 @@
           <t>Share-Based Payments Reserve (note 9)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9122,7 +9126,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -13520,7 +13528,11 @@
           <t>Share-Based Payments Reserve</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -13600,7 +13612,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -14694,7 +14710,11 @@
           <t>Share-Based Payments Reserve (note 9)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -24009,10 +24029,10 @@
         </is>
       </c>
       <c r="P192" s="5" t="n">
-        <v>0.142938</v>
+        <v>-0.142938</v>
       </c>
       <c r="Q192" s="5" t="n">
-        <v>0.308383</v>
+        <v>-0.308383</v>
       </c>
       <c r="R192" t="inlineStr">
         <is>
@@ -26064,10 +26084,10 @@
         </is>
       </c>
       <c r="O216" s="5" t="n">
-        <v>0.398434</v>
+        <v>-0.398434</v>
       </c>
       <c r="P216" s="5" t="n">
-        <v>0.142938</v>
+        <v>-0.142938</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -27423,10 +27443,10 @@
         </is>
       </c>
       <c r="N232" s="5" t="n">
-        <v>0.959657</v>
+        <v>-0.959657</v>
       </c>
       <c r="O232" s="5" t="n">
-        <v>0.398434</v>
+        <v>-0.398434</v>
       </c>
       <c r="P232" t="inlineStr">
         <is>
@@ -30387,16 +30407,16 @@
         </is>
       </c>
       <c r="H267" s="5" t="n">
-        <v>1.510804</v>
+        <v>-1.510804</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>0.519974</v>
+        <v>-0.519974</v>
       </c>
       <c r="J267" s="5" t="n">
-        <v>2.575085</v>
+        <v>-2.575085</v>
       </c>
       <c r="K267" s="5" t="n">
-        <v>0.253756</v>
+        <v>-0.253756</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BMV.xlsx
+++ b/output/pdf_financials_xlsx/BMV.xlsx
@@ -1018,34 +1018,34 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000203</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000284</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000273</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000326</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000242</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000269</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000103</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-8.4e-05</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000451</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000917</v>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
@@ -1923,34 +1923,34 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.510804</v>
+        <v>-1.510601</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.519974</v>
+        <v>-0.51969</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.575085</v>
+        <v>-2.574812</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.575085</v>
+        <v>-2.574759</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.014868</v>
+        <v>-0.014626</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.014868</v>
+        <v>-0.014599</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.959657</v>
+        <v>-0.959554</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.398434</v>
+        <v>-0.39835</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.142938</v>
+        <v>-0.142487</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.308383</v>
+        <v>-0.307466</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -2037,34 +2037,34 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.510804</v>
+        <v>-1.510601</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.519974</v>
+        <v>-0.51969</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.575085</v>
+        <v>-2.574812</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.575085</v>
+        <v>-2.574759</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.014868</v>
+        <v>-0.014626</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.014868</v>
+        <v>-0.014599</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.959657</v>
+        <v>-0.959554</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.398434</v>
+        <v>-0.39835</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.142938</v>
+        <v>-0.142487</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.308383</v>
+        <v>-0.307466</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.253119</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.099274</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.040782</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.244067</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
@@ -2318,25 +2318,25 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000112</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.087893</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.05997</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.011788</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.035368</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.08069</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.037999</v>
       </c>
     </row>
     <row r="35">
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.253119</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.099274</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.040782</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.244067</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
@@ -2416,25 +2416,25 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000112</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.087893</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.05997</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.011788</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.1375</v>
+        <v>0.172868</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.19</v>
+        <v>0.27069</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.19575</v>
+        <v>0.233749</v>
       </c>
     </row>
     <row r="37">
@@ -2983,16 +2983,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.489644</v>
+        <v>0.236525</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.146251</v>
+        <v>0.046977</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.254732</v>
+        <v>0.21395</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.252764</v>
+        <v>0.008697</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.037984</v>
@@ -3004,25 +3004,25 @@
         <v>0.032321</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.001539</v>
+        <v>0.001427</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.091497</v>
+        <v>0.003604</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.06634</v>
+        <v>0.00637</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.033235</v>
+        <v>0.021447</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.044411</v>
+        <v>0.009043000000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.08898499999999999</v>
+        <v>0.008295</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.054845</v>
+        <v>0.016846</v>
       </c>
     </row>
     <row r="49">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -23390,7 +23390,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">

--- a/output/pdf_financials_xlsx/BMV.xlsx
+++ b/output/pdf_financials_xlsx/BMV.xlsx
@@ -546,15 +546,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -603,15 +599,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
@@ -660,15 +652,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
@@ -717,15 +705,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.172576</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.176085</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -774,15 +758,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
@@ -831,15 +811,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.019233</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.009712999999999999</v>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
@@ -888,15 +864,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.191809</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.185798</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -945,15 +917,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.191809</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.185798</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -1002,15 +970,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>-0.022082</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-0.015812</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1059,15 +1023,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
@@ -1116,15 +1076,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
@@ -1173,15 +1129,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
@@ -1230,15 +1182,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0.176627</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.901195</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -1287,15 +1235,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-1.358947</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0.281125</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -1498,15 +1442,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-1.18232</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-1.18232</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1555,15 +1495,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
@@ -1612,15 +1548,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
@@ -1669,15 +1601,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-1.18232</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-1.18232</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -1724,15 +1652,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0.01</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
@@ -1781,15 +1705,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.01</v>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
@@ -1838,10 +1758,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>-19.705333</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1907,15 +1825,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>0.198709</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.885383</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1964,15 +1878,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -2021,15 +1931,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>0.198709</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.885383</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2155,15 +2061,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>769.3880324072763</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-31.19469149296212</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -5720,7 +5622,7 @@
         <v>-0.000421</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0.025563</v>
+        <v>0.03041</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>-0.0262</v>
@@ -6035,7 +5937,7 @@
         <v>0.000388</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.016733</v>
+        <v>0.02158</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0.161988</v>
@@ -6617,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.029425</v>
       </c>
     </row>
     <row r="116">
@@ -7909,7 +7811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R291"/>
+  <dimension ref="A1:R320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17466,7 +17368,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -21816,7 +21722,11 @@
           <t>Loss on write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -23237,15 +23147,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E183" s="5" t="n">
+        <v>0.008855999999999999</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>0.006312</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -29965,15 +29871,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E262" s="5" t="n">
+        <v>0.015016</v>
+      </c>
+      <c r="F262" s="5" t="n">
+        <v>0.010183</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -31845,15 +31747,11 @@
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E284" s="5" t="n">
+        <v>19.644791</v>
+      </c>
+      <c r="F284" s="5" t="n">
+        <v>24.688069</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -32509,6 +32407,2490 @@
         </is>
       </c>
       <c r="R291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Management fees (note 8(a)) $</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="n">
+        <v>0.11595</v>
+      </c>
+      <c r="F292" s="5" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Accounting and audit (note 8(a))</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" s="5" t="n">
+        <v>0.057875</v>
+      </c>
+      <c r="F293" s="5" t="n">
+        <v>0.060432</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Travel (note 8(d))</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="F294" s="5" t="n">
+        <v>0.038696</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>General and office (notes 8(d) and (e))</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" s="5" t="n">
+        <v>0.036933</v>
+      </c>
+      <c r="F295" s="5" t="n">
+        <v>0.032722</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Rent (note 8(e))</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>0.021304</v>
+      </c>
+      <c r="F296" s="5" t="n">
+        <v>0.027894</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Investor relations and communication (note 8(e))</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" s="5" t="n">
+        <v>0.156425</v>
+      </c>
+      <c r="F297" s="5" t="n">
+        <v>0.026793</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Legal (note 8(d))</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="n">
+        <v>0.015149</v>
+      </c>
+      <c r="F298" s="5" t="n">
+        <v>0.007588</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Consulting (note 8(b))</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="n">
+        <v>0.004084</v>
+      </c>
+      <c r="F299" s="5" t="n">
+        <v>0.002125</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (note 7(d))</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" s="5" t="n">
+        <v>0.171067</v>
+      </c>
+      <c r="F300" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Interest and bank charges (recovery)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" s="5" t="n">
+        <v>0.03682</v>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>-0.008808</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Loss Before Other Items and Future Income Tax</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" s="5" t="n">
+        <v>0.650929</v>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>0.296937</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Write-down of mineral property interests (note 5)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" s="5" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="F303" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="n">
+        <v>-0.022082</v>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>-0.015812</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Loss Before Future Income Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="n">
+        <v>1.358947</v>
+      </c>
+      <c r="F305" s="5" t="n">
+        <v>0.281125</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Future Income Tax Recovery (note 10)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="n">
+        <v>-0.176627</v>
+      </c>
+      <c r="F306" s="5" t="n">
+        <v>-0.148373</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for Year $</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="n">
+        <v>-1.18232</v>
+      </c>
+      <c r="F307" s="5" t="n">
+        <v>-0.132752</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Loss Per Common Share, Basic and Diluted $</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="n">
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="F308" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Balance,</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>September 30, 2007 18,021,404 $ 3,038,394 $ 0 $ 579,553 $</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" s="5" t="n">
+        <v>2.717525</v>
+      </c>
+      <c r="F309" s="5" t="n">
+        <v>-0.9004219999999999</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>- private placements</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>(notes 6(b)(i) and (iii)) 2,400,000 600,000 0 0</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F310" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>private placements</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>(notes 6(b)(i) and (iii)) 4,166,665 1,250,000 0 0</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F311" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>property mineral</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>property mineral interest (note 6(b)(ii)) 100,000 30,000 0 0</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F312" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>(notes 6(b)(i) and (iii)) 0 (244,549) 0 61,822</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" s="5" t="n">
+        <v>-0.182727</v>
+      </c>
+      <c r="F313" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>compensation</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>(note 7(d)) 0 0 0 194,575</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" s="5" t="n">
+        <v>0.194575</v>
+      </c>
+      <c r="F314" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Tax benefit renounced -</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Tax benefit renounced - flow-through shares 0 (325,000) 0 0</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" s="5" t="n">
+        <v>-0.325</v>
+      </c>
+      <c r="F315" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Tax benefit renounced -</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Net loss 0 0 0 0</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="n">
+        <v>-1.18232</v>
+      </c>
+      <c r="F316" s="5" t="n">
+        <v>-1.18232</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Balance,</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>September 30, 2008 24,688,069 4,348,845 0 835,950</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" s="5" t="n">
+        <v>3.102053</v>
+      </c>
+      <c r="F317" s="5" t="n">
+        <v>-2.082742</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>of share issue costs</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>(note 13) 0 0 246,047 0</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" s="5" t="n">
+        <v>0.246047</v>
+      </c>
+      <c r="F318" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>of share issue costs</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Net loss 0 0 0 0</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="n">
+        <v>-0.132752</v>
+      </c>
+      <c r="F319" s="5" t="n">
+        <v>-0.132752</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Balance,</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>September 30, 2009 24,688,069 $ 4,348,845 $ 246,047 $ 835,950 $</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" s="5" t="n">
+        <v>3.215348</v>
+      </c>
+      <c r="F320" s="5" t="n">
+        <v>-2.215494</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
         <is>
           <t>-</t>
         </is>
